--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0003T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0003T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.99062673493944</v>
+        <v>11.86097684442766</v>
       </c>
       <c r="D2" t="n">
-        <v>72.96650324222169</v>
+        <v>11.85705677686103</v>
       </c>
       <c r="E2" t="n">
-        <v>10.89719452542334</v>
+        <v>1.770794110381293</v>
       </c>
       <c r="F2" t="n">
-        <v>10.93888471914197</v>
+        <v>1.77756876686057</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.63270046810827</v>
+        <v>9.690313826067595</v>
       </c>
       <c r="D3" t="n">
-        <v>59.54124763814098</v>
+        <v>9.67545274119791</v>
       </c>
       <c r="E3" t="n">
-        <v>10.89719452542334</v>
+        <v>1.770794110381293</v>
       </c>
       <c r="F3" t="n">
-        <v>10.93888471914197</v>
+        <v>1.77756876686057</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.05511733162867</v>
+        <v>7.646456566389658</v>
       </c>
       <c r="D4" t="n">
-        <v>46.96033449988025</v>
+        <v>7.63105435623054</v>
       </c>
       <c r="E4" t="n">
-        <v>10.89719452542334</v>
+        <v>1.770794110381293</v>
       </c>
       <c r="F4" t="n">
-        <v>10.93888471914197</v>
+        <v>1.77756876686057</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.56023130361737</v>
+        <v>7.566037586837823</v>
       </c>
       <c r="D5" t="n">
-        <v>46.5012608653122</v>
+        <v>7.556454890613233</v>
       </c>
       <c r="E5" t="n">
-        <v>10.89719452542334</v>
+        <v>1.770794110381293</v>
       </c>
       <c r="F5" t="n">
-        <v>10.93888471914197</v>
+        <v>1.77756876686057</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>69.00952294830832</v>
+        <v>11.2140474791001</v>
       </c>
       <c r="D6" t="n">
-        <v>69.08803578008272</v>
+        <v>11.22680581426344</v>
       </c>
       <c r="E6" t="n">
-        <v>10.89719452542334</v>
+        <v>1.770794110381293</v>
       </c>
       <c r="F6" t="n">
-        <v>10.93888471914197</v>
+        <v>1.77756876686057</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
